--- a/S15/T174/S15_T174_decision_5.xlsx
+++ b/S15/T174/S15_T174_decision_5.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="72">
   <si>
     <t xml:space="preserve">c1</t>
   </si>
@@ -139,100 +139,100 @@
     <t xml:space="preserve">x 1 batch</t>
   </si>
   <si>
+    <t xml:space="preserve">Rauma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 bin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kemijarvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warsaw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucharest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 20 pallets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cordial production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bottle Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sugar Purchasing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x 1 tonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCFFCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercontinental transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree transport to Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate transport to Arnhem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate transport to Vesoul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FFFF99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production in New-Zeland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madrid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auckland factory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Purchasing and pression of kiwis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x (4 bins of puree  + 1 bin of concentrate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puree sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concentrate sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FF99CC</t>
+  </si>
+  <si>
     <t xml:space="preserve">Berlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puree Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 bin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rauma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kemijarvi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucharest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial packaging</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 20 pallets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warsaw</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cordial production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Milan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bottle Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sugar Purchasing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x 1 tonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate Purchasing for Vesoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CCFFCC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intercontinental transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Madrid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puree transport to Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate transport to Arnhem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate transport to Vesoul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FFFF99</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production in New-Zeland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auckland factory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Purchasing and pression of kiwis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">x (4 bins of puree  + 1 bin of concentrate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puree sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concentrate sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FF99CC</t>
   </si>
   <si>
     <t xml:space="preserve">CCFFFF</t>
@@ -1577,7 +1577,9 @@
       <c r="C11" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="23"/>
+      <c r="D11" s="23" t="n">
+        <v>66</v>
+      </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
       <c r="G11" s="25"/>
@@ -1592,7 +1594,7 @@
         <v>26</v>
       </c>
       <c r="K11" s="28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L11" s="29" t="s">
         <v>27</v>
@@ -1609,7 +1611,9 @@
         <v>29</v>
       </c>
       <c r="D12" s="30"/>
-      <c r="E12" s="31"/>
+      <c r="E12" s="31" t="n">
+        <v>21</v>
+      </c>
       <c r="F12" s="31"/>
       <c r="G12" s="32"/>
       <c r="H12" s="26" t="str">
@@ -1623,7 +1627,7 @@
         <v>30</v>
       </c>
       <c r="K12" s="34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L12" s="35" t="s">
         <v>31</v>
@@ -1653,9 +1657,7 @@
       <c r="J13" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="34"/>
       <c r="L13" s="35" t="s">
         <v>35</v>
       </c>
@@ -1680,9 +1682,7 @@
       <c r="J14" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="K14" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" s="34"/>
       <c r="L14" s="35" t="s">
         <v>35</v>
       </c>
@@ -1692,13 +1692,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C15" s="41" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="31" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="E15" s="31"/>
       <c r="F15" s="31"/>
@@ -1714,7 +1714,7 @@
         <v>37</v>
       </c>
       <c r="K15" s="34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L15" s="35" t="s">
         <v>38</v>
@@ -1725,7 +1725,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C16" s="41" t="s">
         <v>39</v>
@@ -1733,9 +1733,11 @@
       <c r="D16" s="31"/>
       <c r="E16" s="31"/>
       <c r="F16" s="31" t="n">
-        <v>25</v>
-      </c>
-      <c r="G16" s="32"/>
+        <v>15</v>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>10</v>
+      </c>
       <c r="H16" s="26" t="str">
         <f aca="false">IF(AND(B16="",OR(C16&lt;&gt;"",D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A lorry must be selected",IF(AND(C16="",OR(D16&lt;&gt;"",E16&lt;&gt;"",F16&lt;&gt;"",G16&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1746,9 +1748,7 @@
       <c r="J16" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="K16" s="34" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="34"/>
       <c r="L16" s="35" t="s">
         <v>41</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>7</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>42</v>
@@ -1766,9 +1766,11 @@
       <c r="D17" s="31"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31" t="n">
-        <v>25</v>
-      </c>
-      <c r="G17" s="32"/>
+        <v>20</v>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>11</v>
+      </c>
       <c r="H17" s="26" t="str">
         <f aca="false">IF(AND(B17="",OR(C17&lt;&gt;"",D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A lorry must be selected",IF(AND(C17="",OR(D17&lt;&gt;"",E17&lt;&gt;"",F17&lt;&gt;"",G17&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -1779,9 +1781,7 @@
       <c r="J17" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="43" t="n">
-        <v>0</v>
-      </c>
+      <c r="K17" s="43"/>
       <c r="L17" s="44" t="s">
         <v>41</v>
       </c>
@@ -1790,17 +1790,11 @@
       <c r="A18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>44</v>
-      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
-      <c r="F18" s="31" t="n">
-        <v>16</v>
-      </c>
+      <c r="F18" s="31"/>
       <c r="G18" s="32"/>
       <c r="H18" s="26" t="str">
         <f aca="false">IF(AND(B18="",OR(C18&lt;&gt;"",D18&lt;&gt;"",E18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"")),"A lorry must be selected",IF(AND(C18="",OR(D18&lt;&gt;"",E18&lt;&gt;"",F18&lt;&gt;"",G18&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1815,13 +1809,13 @@
         <v>25</v>
       </c>
       <c r="C19" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="31" t="n">
-        <v>66</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D19" s="31"/>
       <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
+      <c r="F19" s="31" t="n">
+        <v>14</v>
+      </c>
       <c r="G19" s="32"/>
       <c r="H19" s="26" t="str">
         <f aca="false">IF(AND(B19="",OR(C19&lt;&gt;"",D19&lt;&gt;"",E19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"")),"A lorry must be selected",IF(AND(C19="",OR(D19&lt;&gt;"",E19&lt;&gt;"",F19&lt;&gt;"",G19&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1844,7 +1838,7 @@
       <c r="D20" s="31"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G20" s="32"/>
       <c r="H20" s="26" t="str">
@@ -1865,7 +1859,7 @@
       <c r="D21" s="31"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G21" s="32"/>
       <c r="H21" s="26" t="str">
@@ -1878,9 +1872,7 @@
       <c r="J21" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="K21" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="K21" s="28"/>
       <c r="L21" s="45" t="s">
         <v>48</v>
       </c>
@@ -1893,13 +1885,13 @@
         <v>25</v>
       </c>
       <c r="C22" s="41" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D22" s="31"/>
-      <c r="E22" s="31"/>
-      <c r="F22" s="31" t="n">
-        <v>20</v>
-      </c>
+      <c r="E22" s="31" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="31"/>
       <c r="G22" s="32"/>
       <c r="H22" s="26" t="str">
         <f aca="false">IF(AND(B22="",OR(C22&lt;&gt;"",D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A lorry must be selected",IF(AND(C22="",OR(D22&lt;&gt;"",E22&lt;&gt;"",F22&lt;&gt;"",G22&lt;&gt;"")),"A town must be selected",""))</f>
@@ -1909,10 +1901,10 @@
         <v>2</v>
       </c>
       <c r="J22" s="46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K22" s="34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" s="46" t="s">
         <v>31</v>
@@ -1922,15 +1914,9 @@
       <c r="A23" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D23" s="31" t="n">
-        <v>66</v>
-      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="31"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
       <c r="G23" s="32"/>
@@ -1958,7 +1944,7 @@
       </c>
       <c r="P23" s="2" t="str">
         <f aca="false">IF(AND(C23&lt;&gt;"",OR(D23&lt;&gt;"",E23&lt;&gt;"",F23&lt;&gt;"",G23&lt;&gt;"")),"A town must be selected","")</f>
-        <v>A town must be selected</v>
+        <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1969,14 +1955,14 @@
         <v>25</v>
       </c>
       <c r="C24" s="41" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D24" s="31"/>
       <c r="E24" s="31"/>
-      <c r="F24" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="G24" s="32"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32" t="n">
+        <v>10</v>
+      </c>
       <c r="H24" s="26" t="str">
         <f aca="false">IF(AND(B24="",OR(C24&lt;&gt;"",D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A lorry must be selected",IF(AND(C24="",OR(D24&lt;&gt;"",E24&lt;&gt;"",F24&lt;&gt;"",G24&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2000,14 +1986,14 @@
         <v>25</v>
       </c>
       <c r="C25" s="41" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D25" s="31"/>
       <c r="E25" s="31"/>
-      <c r="F25" s="31" t="n">
-        <v>33</v>
-      </c>
-      <c r="G25" s="32"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32" t="n">
+        <v>20</v>
+      </c>
       <c r="H25" s="26" t="str">
         <f aca="false">IF(AND(B25="",OR(C25&lt;&gt;"",D25&lt;&gt;"",E25&lt;&gt;"",F25&lt;&gt;"",G25&lt;&gt;"")),"A lorry must be selected",IF(AND(C25="",OR(D25&lt;&gt;"",E25&lt;&gt;"",F25&lt;&gt;"",G25&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2016,10 +2002,10 @@
         <v>5</v>
       </c>
       <c r="J25" s="46" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="K25" s="34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L25" s="46" t="s">
         <v>38</v>
@@ -2029,12 +2015,18 @@
       <c r="A26" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="41"/>
+      <c r="B26" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="41" t="s">
+        <v>46</v>
+      </c>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
+      <c r="G26" s="32" t="n">
+        <v>20</v>
+      </c>
       <c r="H26" s="26" t="str">
         <f aca="false">IF(AND(B26="",OR(C26&lt;&gt;"",D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A lorry must be selected",IF(AND(C26="",OR(D26&lt;&gt;"",E26&lt;&gt;"",F26&lt;&gt;"",G26&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2043,23 +2035,29 @@
         <v>6</v>
       </c>
       <c r="J26" s="46" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K26" s="34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L26" s="46" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
+      <c r="B27" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>29</v>
+      </c>
       <c r="D27" s="31"/>
-      <c r="E27" s="31"/>
+      <c r="E27" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="F27" s="31"/>
       <c r="G27" s="32"/>
       <c r="H27" s="26" t="str">
@@ -2070,11 +2068,9 @@
         <v>7</v>
       </c>
       <c r="J27" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="K27" s="43" t="n">
-        <v>0</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="K27" s="43"/>
       <c r="L27" s="47" t="s">
         <v>41</v>
       </c>
@@ -2083,15 +2079,9 @@
       <c r="A28" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="31"/>
       <c r="F28" s="31"/>
       <c r="G28" s="32"/>
@@ -2100,24 +2090,18 @@
         <v/>
       </c>
       <c r="J28" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B29" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>33</v>
-      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41"/>
       <c r="D29" s="31"/>
       <c r="E29" s="31"/>
-      <c r="F29" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="F29" s="31"/>
       <c r="G29" s="32"/>
       <c r="H29" s="26" t="str">
         <f aca="false">IF(AND(B29="",OR(C29&lt;&gt;"",D29&lt;&gt;"",E29&lt;&gt;"",F29&lt;&gt;"",G29&lt;&gt;"")),"A lorry must be selected",IF(AND(C29="",OR(D29&lt;&gt;"",E29&lt;&gt;"",F29&lt;&gt;"",G29&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2128,15 +2112,9 @@
       <c r="A30" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B30" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="31"/>
       <c r="E30" s="31"/>
       <c r="F30" s="31"/>
       <c r="G30" s="32"/>
@@ -2145,7 +2123,7 @@
         <v/>
       </c>
       <c r="J30" s="48" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K30" s="48"/>
       <c r="L30" s="48"/>
@@ -2158,14 +2136,14 @@
         <v>32</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="D31" s="31"/>
       <c r="E31" s="31"/>
-      <c r="F31" s="31" t="n">
+      <c r="F31" s="31"/>
+      <c r="G31" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="G31" s="32"/>
       <c r="H31" s="26" t="str">
         <f aca="false">IF(AND(B31="",OR(C31&lt;&gt;"",D31&lt;&gt;"",E31&lt;&gt;"",F31&lt;&gt;"",G31&lt;&gt;"")),"A lorry must be selected",IF(AND(C31="",OR(D31&lt;&gt;"",E31&lt;&gt;"",F31&lt;&gt;"",G31&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2175,16 +2153,10 @@
       <c r="A32" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B32" s="40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41"/>
       <c r="D32" s="31"/>
-      <c r="E32" s="31" t="n">
-        <v>24</v>
-      </c>
+      <c r="E32" s="31"/>
       <c r="F32" s="31"/>
       <c r="G32" s="32"/>
       <c r="H32" s="26" t="str">
@@ -2195,10 +2167,10 @@
         <v>1</v>
       </c>
       <c r="J32" s="49" t="s">
+        <v>56</v>
+      </c>
+      <c r="K32" s="28" t="n">
         <v>60</v>
-      </c>
-      <c r="K32" s="28" t="n">
-        <v>20</v>
       </c>
       <c r="L32" s="49" t="s">
         <v>41</v>
@@ -2212,14 +2184,14 @@
         <v>32</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="E33" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="F33" s="31"/>
-      <c r="G33" s="32" t="n">
-        <v>24</v>
-      </c>
+      <c r="G33" s="32"/>
       <c r="H33" s="26" t="str">
         <f aca="false">IF(AND(B33="",OR(C33&lt;&gt;"",D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A lorry must be selected",IF(AND(C33="",OR(D33&lt;&gt;"",E33&lt;&gt;"",F33&lt;&gt;"",G33&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2228,9 +2200,11 @@
         <v>2</v>
       </c>
       <c r="J33" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="K33" s="34"/>
+        <v>57</v>
+      </c>
+      <c r="K33" s="34" t="n">
+        <v>17</v>
+      </c>
       <c r="L33" s="50" t="s">
         <v>41</v>
       </c>
@@ -2239,12 +2213,18 @@
       <c r="A34" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B34" s="40"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>58</v>
+      </c>
       <c r="D34" s="31"/>
       <c r="E34" s="31"/>
       <c r="F34" s="31"/>
-      <c r="G34" s="32"/>
+      <c r="G34" s="32" t="n">
+        <v>12</v>
+      </c>
       <c r="H34" s="26" t="str">
         <f aca="false">IF(AND(B34="",OR(C34&lt;&gt;"",D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A lorry must be selected",IF(AND(C34="",OR(D34&lt;&gt;"",E34&lt;&gt;"",F34&lt;&gt;"",G34&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2253,10 +2233,10 @@
         <v>3</v>
       </c>
       <c r="J34" s="51" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K34" s="43" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L34" s="51" t="s">
         <v>41</v>
@@ -2266,18 +2246,24 @@
       <c r="A35" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="41"/>
+      <c r="B35" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>60</v>
+      </c>
       <c r="D35" s="31"/>
       <c r="E35" s="31"/>
       <c r="F35" s="31"/>
-      <c r="G35" s="32"/>
+      <c r="G35" s="32" t="n">
+        <v>12</v>
+      </c>
       <c r="H35" s="26" t="str">
         <f aca="false">IF(AND(B35="",OR(C35&lt;&gt;"",D35&lt;&gt;"",E35&lt;&gt;"",F35&lt;&gt;"",G35&lt;&gt;"")),"A lorry must be selected",IF(AND(C35="",OR(D35&lt;&gt;"",E35&lt;&gt;"",F35&lt;&gt;"",G35&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J35" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,14 +2271,14 @@
         <v>26</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C36" s="41" t="s">
         <v>29</v>
       </c>
       <c r="D36" s="31"/>
       <c r="E36" s="31" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F36" s="31"/>
       <c r="G36" s="32"/>
@@ -2305,24 +2291,18 @@
       <c r="A37" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B37" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>39</v>
-      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41"/>
       <c r="D37" s="31"/>
       <c r="E37" s="31"/>
       <c r="F37" s="31"/>
-      <c r="G37" s="32" t="n">
-        <v>12</v>
-      </c>
+      <c r="G37" s="32"/>
       <c r="H37" s="26" t="str">
         <f aca="false">IF(AND(B37="",OR(C37&lt;&gt;"",D37&lt;&gt;"",E37&lt;&gt;"",F37&lt;&gt;"",G37&lt;&gt;"")),"A lorry must be selected",IF(AND(C37="",OR(D37&lt;&gt;"",E37&lt;&gt;"",F37&lt;&gt;"",G37&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J37" s="52" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K37" s="52"/>
       <c r="L37" s="52"/>
@@ -2332,16 +2312,16 @@
         <v>28</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="D38" s="31"/>
       <c r="E38" s="31"/>
       <c r="F38" s="31"/>
       <c r="G38" s="32" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H38" s="26" t="str">
         <f aca="false">IF(AND(B38="",OR(C38&lt;&gt;"",D38&lt;&gt;"",E38&lt;&gt;"",F38&lt;&gt;"",G38&lt;&gt;"")),"A lorry must be selected",IF(AND(C38="",OR(D38&lt;&gt;"",E38&lt;&gt;"",F38&lt;&gt;"",G38&lt;&gt;"")),"A town must be selected",""))</f>
@@ -2352,40 +2332,28 @@
       <c r="A39" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B39" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>44</v>
-      </c>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41"/>
       <c r="D39" s="31"/>
       <c r="E39" s="31"/>
       <c r="F39" s="31"/>
-      <c r="G39" s="32" t="n">
-        <v>23</v>
-      </c>
+      <c r="G39" s="32"/>
       <c r="H39" s="26" t="str">
         <f aca="false">IF(AND(B39="",OR(C39&lt;&gt;"",D39&lt;&gt;"",E39&lt;&gt;"",F39&lt;&gt;"",G39&lt;&gt;"")),"A lorry must be selected",IF(AND(C39="",OR(D39&lt;&gt;"",E39&lt;&gt;"",F39&lt;&gt;"",G39&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J39" s="53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B40" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="41" t="s">
-        <v>29</v>
-      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41"/>
       <c r="D40" s="31"/>
-      <c r="E40" s="31" t="n">
-        <v>50</v>
-      </c>
+      <c r="E40" s="31"/>
       <c r="F40" s="31"/>
       <c r="G40" s="32"/>
       <c r="H40" s="26" t="str">
@@ -2398,17 +2366,17 @@
         <v>31</v>
       </c>
       <c r="B41" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C41" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="D41" s="31"/>
+        <v>22</v>
+      </c>
+      <c r="D41" s="31" t="n">
+        <v>66</v>
+      </c>
       <c r="E41" s="31"/>
       <c r="F41" s="31"/>
-      <c r="G41" s="32" t="n">
-        <v>10</v>
-      </c>
+      <c r="G41" s="32"/>
       <c r="H41" s="26" t="str">
         <f aca="false">IF(AND(B41="",OR(C41&lt;&gt;"",D41&lt;&gt;"",E41&lt;&gt;"",F41&lt;&gt;"",G41&lt;&gt;"")),"A lorry must be selected",IF(AND(C41="",OR(D41&lt;&gt;"",E41&lt;&gt;"",F41&lt;&gt;"",G41&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2417,13 +2385,13 @@
         <v>1</v>
       </c>
       <c r="J41" s="55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K41" s="28" t="n">
         <v>15</v>
       </c>
       <c r="L41" s="55" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M41" s="56"/>
     </row>
@@ -2432,17 +2400,17 @@
         <v>32</v>
       </c>
       <c r="B42" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D42" s="31"/>
       <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="32" t="n">
-        <v>20</v>
-      </c>
+      <c r="F42" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G42" s="32"/>
       <c r="H42" s="26" t="str">
         <f aca="false">IF(AND(B42="",OR(C42&lt;&gt;"",D42&lt;&gt;"",E42&lt;&gt;"",F42&lt;&gt;"",G42&lt;&gt;"")),"A lorry must be selected",IF(AND(C42="",OR(D42&lt;&gt;"",E42&lt;&gt;"",F42&lt;&gt;"",G42&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2463,17 +2431,17 @@
         <v>33</v>
       </c>
       <c r="B43" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="D43" s="31"/>
       <c r="E43" s="31"/>
-      <c r="F43" s="31"/>
-      <c r="G43" s="32" t="n">
-        <v>20</v>
-      </c>
+      <c r="F43" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G43" s="32"/>
       <c r="H43" s="26" t="str">
         <f aca="false">IF(AND(B43="",OR(C43&lt;&gt;"",D43&lt;&gt;"",E43&lt;&gt;"",F43&lt;&gt;"",G43&lt;&gt;"")),"A lorry must be selected",IF(AND(C43="",OR(D43&lt;&gt;"",E43&lt;&gt;"",F43&lt;&gt;"",G43&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2494,15 +2462,15 @@
         <v>34</v>
       </c>
       <c r="B44" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="31"/>
-      <c r="E44" s="31" t="n">
-        <v>17</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D44" s="31" t="n">
+        <v>66</v>
+      </c>
+      <c r="E44" s="31"/>
       <c r="F44" s="31"/>
       <c r="G44" s="32"/>
       <c r="H44" s="26" t="str">
@@ -2513,10 +2481,10 @@
         <v>4</v>
       </c>
       <c r="J44" s="57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K44" s="34" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="L44" s="57" t="s">
         <v>41</v>
@@ -2527,17 +2495,17 @@
         <v>35</v>
       </c>
       <c r="B45" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D45" s="31"/>
       <c r="E45" s="31"/>
-      <c r="F45" s="31"/>
-      <c r="G45" s="32" t="n">
-        <v>8</v>
-      </c>
+      <c r="F45" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G45" s="32"/>
       <c r="H45" s="26" t="str">
         <f aca="false">IF(AND(B45="",OR(C45&lt;&gt;"",D45&lt;&gt;"",E45&lt;&gt;"",F45&lt;&gt;"",G45&lt;&gt;"")),"A lorry must be selected",IF(AND(C45="",OR(D45&lt;&gt;"",E45&lt;&gt;"",F45&lt;&gt;"",G45&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2546,7 +2514,7 @@
         <v>5</v>
       </c>
       <c r="J45" s="58" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K45" s="43"/>
       <c r="L45" s="58" t="s">
@@ -2558,23 +2526,23 @@
         <v>36</v>
       </c>
       <c r="B46" s="40" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D46" s="31"/>
       <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="32" t="n">
-        <v>9</v>
-      </c>
+      <c r="F46" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="G46" s="32"/>
       <c r="H46" s="26" t="str">
         <f aca="false">IF(AND(B46="",OR(C46&lt;&gt;"",D46&lt;&gt;"",E46&lt;&gt;"",F46&lt;&gt;"",G46&lt;&gt;"")),"A lorry must be selected",IF(AND(C46="",OR(D46&lt;&gt;"",E46&lt;&gt;"",F46&lt;&gt;"",G46&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
       </c>
       <c r="J46" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2596,10 +2564,16 @@
       <c r="A48" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B48" s="40"/>
-      <c r="C48" s="41"/>
+      <c r="B48" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>29</v>
+      </c>
       <c r="D48" s="31"/>
-      <c r="E48" s="31"/>
+      <c r="E48" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="F48" s="31"/>
       <c r="G48" s="32"/>
       <c r="H48" s="26" t="str">
@@ -2611,12 +2585,18 @@
       <c r="A49" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B49" s="40"/>
-      <c r="C49" s="41"/>
+      <c r="B49" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>70</v>
+      </c>
       <c r="D49" s="31"/>
       <c r="E49" s="31"/>
       <c r="F49" s="31"/>
-      <c r="G49" s="32"/>
+      <c r="G49" s="32" t="n">
+        <v>24</v>
+      </c>
       <c r="H49" s="26" t="str">
         <f aca="false">IF(AND(B49="",OR(C49&lt;&gt;"",D49&lt;&gt;"",E49&lt;&gt;"",F49&lt;&gt;"",G49&lt;&gt;"")),"A lorry must be selected",IF(AND(C49="",OR(D49&lt;&gt;"",E49&lt;&gt;"",F49&lt;&gt;"",G49&lt;&gt;"")),"A town must be selected",""))</f>
         <v/>
@@ -2626,9 +2606,15 @@
       <c r="A50" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B50" s="40"/>
-      <c r="C50" s="41"/>
-      <c r="D50" s="31"/>
+      <c r="B50" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D50" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="E50" s="31"/>
       <c r="F50" s="31"/>
       <c r="G50" s="32"/>
@@ -2641,11 +2627,17 @@
       <c r="A51" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B51" s="40"/>
-      <c r="C51" s="41"/>
+      <c r="B51" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="41" t="s">
+        <v>70</v>
+      </c>
       <c r="D51" s="31"/>
       <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
+      <c r="F51" s="31" t="n">
+        <v>24</v>
+      </c>
       <c r="G51" s="32"/>
       <c r="H51" s="26" t="str">
         <f aca="false">IF(AND(B51="",OR(C51&lt;&gt;"",D51&lt;&gt;"",E51&lt;&gt;"",F51&lt;&gt;"",G51&lt;&gt;"")),"A lorry must be selected",IF(AND(C51="",OR(D51&lt;&gt;"",E51&lt;&gt;"",F51&lt;&gt;"",G51&lt;&gt;"")),"A town must be selected",""))</f>
